--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.67011850997655</v>
+        <v>9.858894257871189</v>
       </c>
       <c r="D2" t="n">
-        <v>19.50035735862801</v>
+        <v>3.168808070777052</v>
       </c>
       <c r="E2" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F2" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.73281908243454</v>
+        <v>9.869083100895613</v>
       </c>
       <c r="D3" t="n">
-        <v>26.00836852650496</v>
+        <v>4.226359885557057</v>
       </c>
       <c r="E3" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F3" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.62521257590871</v>
+        <v>12.61409704358516</v>
       </c>
       <c r="D4" t="n">
-        <v>25.44967838368643</v>
+        <v>4.135572737349046</v>
       </c>
       <c r="E4" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F4" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.11536657722746</v>
+        <v>9.443747068799462</v>
       </c>
       <c r="D5" t="n">
-        <v>37.58477108299466</v>
+        <v>6.107525300986632</v>
       </c>
       <c r="E5" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F5" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.67630894495129</v>
+        <v>6.284900203554586</v>
       </c>
       <c r="D6" t="n">
-        <v>22.73510359352039</v>
+        <v>3.694454333947063</v>
       </c>
       <c r="E6" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F6" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.82339646707678</v>
+        <v>10.37130192589998</v>
       </c>
       <c r="D7" t="n">
-        <v>53.72090015289159</v>
+        <v>8.729646274844885</v>
       </c>
       <c r="E7" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F7" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.36519924705652</v>
+        <v>6.721844877646685</v>
       </c>
       <c r="D8" t="n">
-        <v>30.77428494884024</v>
+        <v>5.00082130418654</v>
       </c>
       <c r="E8" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F8" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.24696121174073</v>
+        <v>2.152631196907869</v>
       </c>
       <c r="D9" t="n">
-        <v>10.35656461875646</v>
+        <v>1.682941750547925</v>
       </c>
       <c r="E9" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F9" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.37009429444541</v>
+        <v>10.78514032284738</v>
       </c>
       <c r="D10" t="n">
-        <v>61.78471897825941</v>
+        <v>10.04001683396715</v>
       </c>
       <c r="E10" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F10" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.43137784030657</v>
+        <v>9.007598899049819</v>
       </c>
       <c r="D11" t="n">
-        <v>50.94465883191064</v>
+        <v>8.278507060185479</v>
       </c>
       <c r="E11" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F11" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.53531661240551</v>
+        <v>3.336988949515896</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12676450605966</v>
+        <v>4.408099232234695</v>
       </c>
       <c r="E12" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F12" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.20899505287495</v>
+        <v>7.833961696092181</v>
       </c>
       <c r="D13" t="n">
-        <v>53.67613156697807</v>
+        <v>8.722371379633937</v>
       </c>
       <c r="E13" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F13" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>49.80973084143535</v>
+        <v>8.094081261733244</v>
       </c>
       <c r="D14" t="n">
-        <v>47.26493283962952</v>
+        <v>7.680551586439797</v>
       </c>
       <c r="E14" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F14" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.3118982820439</v>
+        <v>4.925683470832134</v>
       </c>
       <c r="D15" t="n">
-        <v>38.04757527379743</v>
+        <v>6.182730981992083</v>
       </c>
       <c r="E15" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F15" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.72136163877335</v>
+        <v>3.20472126630067</v>
       </c>
       <c r="D16" t="n">
-        <v>28.62254356272342</v>
+        <v>4.651163328942556</v>
       </c>
       <c r="E16" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F16" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>46.14124998089104</v>
+        <v>7.497953121894795</v>
       </c>
       <c r="D17" t="n">
-        <v>36.87817782917155</v>
+        <v>5.992703897240377</v>
       </c>
       <c r="E17" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F17" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.55543816114361</v>
+        <v>6.427758701185837</v>
       </c>
       <c r="D18" t="n">
-        <v>26.57536453183662</v>
+        <v>4.318496736423452</v>
       </c>
       <c r="E18" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F18" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>45.61718025568744</v>
+        <v>7.412791791549209</v>
       </c>
       <c r="D19" t="n">
-        <v>30.30264014900352</v>
+        <v>4.924179024213072</v>
       </c>
       <c r="E19" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F19" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>13.8225767993279</v>
+        <v>2.246168729890784</v>
       </c>
       <c r="D20" t="n">
-        <v>19.74881384110887</v>
+        <v>3.209182249180192</v>
       </c>
       <c r="E20" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F20" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>65.53602438444382</v>
+        <v>10.64960396247212</v>
       </c>
       <c r="D21" t="n">
-        <v>11.62847941551208</v>
+        <v>1.889627905020713</v>
       </c>
       <c r="E21" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F21" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>18.08197789347018</v>
+        <v>2.938321407688905</v>
       </c>
       <c r="D22" t="n">
-        <v>24.61446352693617</v>
+        <v>3.999850323127128</v>
       </c>
       <c r="E22" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F22" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>44.23832406011587</v>
+        <v>7.188727659768829</v>
       </c>
       <c r="D23" t="n">
-        <v>17.20952853318605</v>
+        <v>2.796548386642733</v>
       </c>
       <c r="E23" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F23" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>24.34947561461337</v>
+        <v>3.956789787374673</v>
       </c>
       <c r="D24" t="n">
-        <v>15.82780336380865</v>
+        <v>2.572018046618906</v>
       </c>
       <c r="E24" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F24" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>61.80363851204309</v>
+        <v>10.043091258207</v>
       </c>
       <c r="D25" t="n">
-        <v>4.956659033935665</v>
+        <v>0.8054570930145456</v>
       </c>
       <c r="E25" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F25" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>72.33114143666046</v>
+        <v>11.75381048345733</v>
       </c>
       <c r="D26" t="n">
-        <v>7.067446939614107</v>
+        <v>1.148460127687292</v>
       </c>
       <c r="E26" t="n">
-        <v>18.76012969906065</v>
+        <v>3.048521076097356</v>
       </c>
       <c r="F26" t="n">
-        <v>14.99124322627303</v>
+        <v>2.436077024269367</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
